--- a/Result/profitability/4113.xlsx
+++ b/Result/profitability/4113.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,11 +663,11 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.03624999999999998</v>
+        <v>-0.07375000000000002</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -766,11 +766,11 @@
         <v>-0.1</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.05625000000000003</v>
+        <v>-0.125</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -875,7 +875,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.10375</v>
+        <v>-0.14125</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
@@ -988,7 +988,7 @@
         <v>-0.11</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.125</v>
+        <v>-0.1475</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
@@ -1101,7 +1101,7 @@
         <v>0.17</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.09625000000000003</v>
+        <v>-0.105</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
@@ -1224,7 +1224,7 @@
         <v>0.98</v>
       </c>
       <c r="M7" t="n">
-        <v>0.04749999999999997</v>
+        <v>0.05124999999999998</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
@@ -1345,7 +1345,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>0.19875</v>
+        <v>0.19625</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
@@ -9772,6 +9772,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4113</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>166</v>
+      </c>
+      <c r="D75" t="n">
+        <v>139</v>
+      </c>
+      <c r="E75" t="n">
+        <v>27</v>
+      </c>
+      <c r="F75" t="n">
+        <v>16.17</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-10</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-5.78%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-46</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-55</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-56</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.006249999999999974</v>
+      </c>
+      <c r="N75" t="n">
+        <v>29.76</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.01999999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.09090909090909083</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-28.34</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.6367108514940463</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-12.74</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.4406779661016949</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
